--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3979" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3675" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profiling of the FHIR Vital Sign Heart Rate Profile.
+    <t>French profile for the FHIR Vital Sign Heart Rate Profile.
 Profilage français du profil Vital Signs Heart rate</t>
   </si>
   <si>
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/heartrate</t>
+    <t>http://hl7.org/fhir/StructureDefinition/heartrate|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -459,14 +459,14 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,6 +488,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-heartrate|2.2.0</t>
+  </si>
+  <si>
     <t>Observation.meta.security</t>
   </si>
   <si>
@@ -510,7 +513,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -534,7 +537,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -577,7 +580,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -653,14 +656,15 @@
     <t>levelOfExertion</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-level-of-exertion}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-level-of-exertion|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Observation Level Of Exertion Extension</t>
   </si>
   <si>
-    <t>French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure | Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort)</t>
+    <t>Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort).
+French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -673,14 +677,15 @@
     <t>bodyPosition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-position-ext}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-position-ext|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Observation Body Position Ext Extension</t>
   </si>
   <si>
-    <t>CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation | Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.</t>
+    <t>Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.
+CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation</t>
   </si>
   <si>
     <t>Observation.extension:supportingInfo</t>
@@ -689,7 +694,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
 </t>
   </si>
   <si>
@@ -750,7 +755,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -779,7 +784,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -859,7 +864,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1114,7 +1119,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1208,7 +1213,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1239,7 +1244,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1262,7 +1267,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -1357,7 +1362,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0)
 </t>
   </si>
   <si>
@@ -1598,7 +1603,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1630,7 +1635,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1683,7 +1688,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/hspc/ValueSet/heartRateMeasBodyLocationPrecoordVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heartrate-body-location|2.2.0</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1698,21 +1703,6 @@
     <t>718497002 |Inherent location|</t>
   </si>
   <si>
-    <t>Observation.bodySite.id</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heart-rate-body-position</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.text</t>
-  </si>
-  <si>
     <t>Observation.method</t>
   </si>
   <si>
@@ -1731,7 +1721,7 @@
     <t>Methods for heartrate observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/hspc/ValueSet/heartRateMeasMethodVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heartrate-measurement-method|2.2.0</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1740,25 +1730,10 @@
     <t>methodCode</t>
   </si>
   <si>
-    <t>Observation.method.id</t>
-  </si>
-  <si>
-    <t>Observation.method.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heart-rate-method</t>
-  </si>
-  <si>
-    <t>Observation.method.text</t>
-  </si>
-  <si>
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1786,7 +1761,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1866,7 +1841,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1916,7 +1891,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1949,7 +1924,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1986,7 +1961,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2008,7 +1983,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2454,18 +2429,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP103"/>
+  <dimension ref="A1:AP95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.9296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.5625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.12109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2476,28 +2451,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.26171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.984375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.30078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3754,7 +3729,7 @@
         <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>83</v>
@@ -3828,10 +3803,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3854,16 +3829,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3889,13 +3864,13 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>83</v>
@@ -3913,7 +3888,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3948,10 +3923,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3974,16 +3949,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4009,13 +3984,13 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>83</v>
@@ -4033,7 +4008,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -4068,10 +4043,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4097,13 +4072,13 @@
         <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4153,7 +4128,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4188,10 +4163,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4214,16 +4189,16 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4249,13 +4224,13 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
@@ -4273,7 +4248,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4308,14 +4283,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4334,16 +4309,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4393,7 +4368,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4417,7 +4392,7 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
@@ -4428,14 +4403,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4454,16 +4429,16 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4513,7 +4488,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4537,7 +4512,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4548,10 +4523,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4577,10 +4552,10 @@
         <v>115</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4629,7 +4604,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4664,13 +4639,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>83</v>
@@ -4692,13 +4667,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4749,7 +4724,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4758,7 +4733,7 @@
         <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>123</v>
@@ -4784,13 +4759,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>83</v>
@@ -4812,13 +4787,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4869,7 +4844,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4878,7 +4853,7 @@
         <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>123</v>
@@ -4902,15 +4877,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>83</v>
@@ -4932,13 +4907,13 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4989,7 +4964,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -5024,10 +4999,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5053,16 +5028,16 @@
         <v>115</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -5111,7 +5086,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5135,7 +5110,7 @@
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -5146,10 +5121,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5172,17 +5147,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -5231,7 +5206,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5246,19 +5221,19 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
@@ -5266,14 +5241,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5292,17 +5267,17 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5351,7 +5326,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5366,16 +5341,16 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5386,14 +5361,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5412,16 +5387,16 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5471,7 +5446,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5486,16 +5461,16 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5504,12 +5479,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5532,19 +5507,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5569,11 +5544,11 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5591,7 +5566,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>94</v>
@@ -5606,19 +5581,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
@@ -5626,10 +5601,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5652,19 +5627,19 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5689,19 +5664,19 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
@@ -5711,7 +5686,7 @@
         <v>121</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5735,24 +5710,24 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5774,19 +5749,19 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5811,13 +5786,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5835,7 +5810,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5859,10 +5834,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5870,10 +5845,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5988,10 +5963,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6106,12 +6081,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6134,19 +6109,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -6195,7 +6170,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6216,10 +6191,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6230,10 +6205,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6348,10 +6323,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6466,12 +6441,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6497,23 +6472,23 @@
         <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6555,7 +6530,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6576,10 +6551,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6590,10 +6565,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6619,13 +6594,13 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6675,7 +6650,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6696,10 +6671,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6708,12 +6683,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6736,24 +6711,24 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6795,7 +6770,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6816,10 +6791,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6830,10 +6805,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6859,14 +6834,14 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6915,7 +6890,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6936,10 +6911,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6950,10 +6925,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6976,19 +6951,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -7037,7 +7012,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7058,10 +7033,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -7072,10 +7047,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7101,16 +7076,16 @@
         <v>108</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7159,7 +7134,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7180,10 +7155,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -7192,16 +7167,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7220,19 +7195,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7257,13 +7232,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7281,7 +7256,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -7296,30 +7271,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7434,10 +7409,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7554,10 +7529,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7580,19 +7555,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7629,7 +7604,7 @@
         <v>83</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7639,7 +7614,7 @@
         <v>121</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7660,10 +7635,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7674,13 +7649,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>83</v>
@@ -7702,19 +7677,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7763,7 +7738,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7784,10 +7759,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7798,10 +7773,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7916,10 +7891,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8036,10 +8011,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8065,23 +8040,23 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -8123,7 +8098,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8144,10 +8119,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8158,10 +8133,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8187,13 +8162,13 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8243,7 +8218,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8264,10 +8239,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8278,10 +8253,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8304,24 +8279,24 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>83</v>
@@ -8363,7 +8338,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8384,10 +8359,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8398,10 +8373,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8427,14 +8402,14 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8483,7 +8458,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8504,10 +8479,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8518,10 +8493,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8544,19 +8519,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8605,7 +8580,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8626,10 +8601,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8640,10 +8615,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8669,16 +8644,16 @@
         <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8727,7 +8702,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8748,10 +8723,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8760,12 +8735,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8788,19 +8763,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8849,7 +8824,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8864,19 +8839,19 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8884,10 +8859,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8910,16 +8885,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8969,7 +8944,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8990,13 +8965,13 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -9004,14 +8979,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9030,19 +9005,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9091,7 +9066,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9106,34 +9081,34 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9152,19 +9127,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9213,7 +9188,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9222,25 +9197,25 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9248,10 +9223,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9277,13 +9252,13 @@
         <v>130</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9333,7 +9308,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9354,13 +9329,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9368,10 +9343,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9394,17 +9369,17 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9453,7 +9428,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9468,19 +9443,19 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -9488,10 +9463,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9514,19 +9489,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9563,17 +9538,17 @@
         <v>83</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9582,7 +9557,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9591,30 +9566,30 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>83</v>
@@ -9636,19 +9611,19 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9697,7 +9672,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9706,7 +9681,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9715,27 +9690,27 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9850,10 +9825,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9968,12 +9943,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9996,19 +9971,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10057,7 +10032,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10078,10 +10053,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -10092,10 +10067,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10118,23 +10093,23 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="R64" t="s" s="2">
         <v>83</v>
@@ -10155,13 +10130,13 @@
         <v>83</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -10179,7 +10154,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10200,10 +10175,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10212,12 +10187,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10243,14 +10218,14 @@
         <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10299,7 +10274,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10320,10 +10295,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10332,12 +10307,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10363,21 +10338,21 @@
         <v>136</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>83</v>
@@ -10419,7 +10394,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10428,7 +10403,7 @@
         <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>106</v>
@@ -10440,10 +10415,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10452,12 +10427,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10480,26 +10455,26 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>83</v>
@@ -10541,7 +10516,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10562,10 +10537,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10574,12 +10549,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10602,19 +10577,19 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10639,13 +10614,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10663,7 +10638,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10672,7 +10647,7 @@
         <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -10684,10 +10659,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10698,14 +10673,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10724,19 +10699,19 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10761,13 +10736,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10785,7 +10760,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10803,27 +10778,27 @@
         <v>83</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10846,19 +10821,19 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10907,7 +10882,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10928,10 +10903,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10942,10 +10917,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10968,16 +10943,16 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11003,11 +10978,11 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11025,7 +11000,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11043,27 +11018,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11086,16 +11061,20 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>108</v>
+        <v>264</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>109</v>
+        <v>543</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
       </c>
@@ -11119,13 +11098,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>83</v>
+        <v>548</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -11143,7 +11122,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>111</v>
+        <v>542</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11155,7 +11134,7 @@
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -11164,10 +11143,10 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>83</v>
+        <v>549</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>112</v>
+        <v>550</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -11178,21 +11157,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>83</v>
@@ -11204,16 +11183,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>115</v>
+        <v>552</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>116</v>
+        <v>553</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>117</v>
+        <v>554</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>118</v>
+        <v>555</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11251,57 +11230,57 @@
         <v>83</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>122</v>
+        <v>551</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>83</v>
+        <v>556</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>112</v>
+        <v>558</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>83</v>
+        <v>559</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11312,7 +11291,7 @@
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
@@ -11321,23 +11300,21 @@
         <v>83</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>152</v>
+        <v>561</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>281</v>
+        <v>562</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>282</v>
+        <v>563</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>83</v>
       </c>
@@ -11361,11 +11338,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11383,13 +11362,13 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>285</v>
+        <v>560</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>83</v>
@@ -11401,27 +11380,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>83</v>
+        <v>565</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>286</v>
+        <v>566</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>287</v>
+        <v>567</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>83</v>
+        <v>568</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11432,7 +11411,7 @@
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>83</v>
@@ -11441,22 +11420,22 @@
         <v>83</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>108</v>
+        <v>570</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>339</v>
+        <v>571</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>340</v>
+        <v>572</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>341</v>
+        <v>573</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>342</v>
+        <v>574</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11505,19 +11484,19 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>343</v>
+        <v>569</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>106</v>
+        <v>575</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>83</v>
@@ -11526,10 +11505,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>344</v>
+        <v>576</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>345</v>
+        <v>577</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11540,10 +11519,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11566,20 +11545,16 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>263</v>
+        <v>108</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>547</v>
+        <v>109</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
@@ -11603,13 +11578,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>551</v>
+        <v>83</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>552</v>
+        <v>83</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11627,7 +11602,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>546</v>
+        <v>111</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11639,7 +11614,7 @@
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
@@ -11648,10 +11623,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>553</v>
+        <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>554</v>
+        <v>112</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11662,21 +11637,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11688,15 +11663,17 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11745,19 +11722,19 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>83</v>
@@ -11780,14 +11757,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>556</v>
+        <v>580</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>556</v>
+        <v>580</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>114</v>
+        <v>581</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11800,24 +11777,26 @@
         <v>83</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>115</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>116</v>
+        <v>582</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>117</v>
+        <v>583</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11853,19 +11832,19 @@
         <v>83</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>122</v>
+        <v>584</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11889,7 +11868,7 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>112</v>
+        <v>198</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11900,10 +11879,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11914,7 +11893,7 @@
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>83</v>
@@ -11923,23 +11902,19 @@
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>152</v>
+        <v>586</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>281</v>
+        <v>587</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -11963,11 +11938,13 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>558</v>
+        <v>83</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -11985,16 +11962,16 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>285</v>
+        <v>585</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>83</v>
+        <v>589</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -12006,10 +11983,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>286</v>
+        <v>590</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>287</v>
+        <v>591</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -12020,10 +11997,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>559</v>
+        <v>592</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>559</v>
+        <v>592</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12043,23 +12020,19 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>108</v>
+        <v>586</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>339</v>
+        <v>593</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12107,7 +12080,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>343</v>
+        <v>592</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12116,7 +12089,7 @@
         <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>83</v>
+        <v>589</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>106</v>
@@ -12128,10 +12101,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>344</v>
+        <v>590</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>345</v>
+        <v>595</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12142,10 +12115,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12168,18 +12141,20 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>561</v>
+        <v>264</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>562</v>
+        <v>597</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>563</v>
+        <v>598</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
@@ -12203,13 +12178,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>83</v>
+        <v>601</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>83</v>
+        <v>602</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12227,7 +12202,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12245,27 +12220,27 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>565</v>
+        <v>603</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>566</v>
+        <v>604</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>567</v>
+        <v>523</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>568</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12276,7 +12251,7 @@
         <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>83</v>
@@ -12288,18 +12263,20 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>570</v>
+        <v>264</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>571</v>
+        <v>606</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>572</v>
+        <v>607</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -12323,13 +12300,13 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>83</v>
+        <v>610</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>83</v>
+        <v>611</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12347,13 +12324,13 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>83</v>
@@ -12365,27 +12342,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>574</v>
+        <v>603</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>575</v>
+        <v>604</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>576</v>
+        <v>523</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>577</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12396,7 +12373,7 @@
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12408,19 +12385,17 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>579</v>
+        <v>613</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>580</v>
+        <v>614</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12469,19 +12444,19 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>584</v>
+        <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
@@ -12490,10 +12465,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>585</v>
+        <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12504,10 +12479,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12533,10 +12508,10 @@
         <v>108</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>109</v>
+        <v>619</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>110</v>
+        <v>620</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12587,7 +12562,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>111</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12599,7 +12574,7 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12608,10 +12583,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>83</v>
+        <v>590</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>112</v>
+        <v>621</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12622,14 +12597,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>588</v>
+        <v>622</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>588</v>
+        <v>622</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12645,19 +12620,19 @@
         <v>83</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>115</v>
+        <v>623</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>116</v>
+        <v>624</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>117</v>
+        <v>625</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>118</v>
+        <v>626</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12707,7 +12682,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>122</v>
+        <v>622</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12719,7 +12694,7 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
@@ -12728,10 +12703,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>83</v>
+        <v>627</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>112</v>
+        <v>628</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12742,14 +12717,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>589</v>
+        <v>629</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>589</v>
+        <v>629</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>590</v>
+        <v>83</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12762,26 +12737,24 @@
         <v>83</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>115</v>
+        <v>630</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>591</v>
+        <v>631</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>592</v>
+        <v>632</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12829,7 +12802,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>593</v>
+        <v>629</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12841,7 +12814,7 @@
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12850,10 +12823,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>83</v>
+        <v>627</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>197</v>
+        <v>634</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12862,12 +12835,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12878,28 +12851,32 @@
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>596</v>
+        <v>636</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>636</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>638</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -12947,19 +12924,19 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>598</v>
+        <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>639</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>83</v>
@@ -12968,10 +12945,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>599</v>
+        <v>640</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>600</v>
+        <v>641</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12982,10 +12959,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>601</v>
+        <v>642</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>601</v>
+        <v>642</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13008,13 +12985,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>595</v>
+        <v>108</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>602</v>
+        <v>109</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>603</v>
+        <v>110</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13065,7 +13042,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>601</v>
+        <v>111</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13074,10 +13051,10 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>598</v>
+        <v>83</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>83</v>
@@ -13086,10 +13063,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>599</v>
+        <v>83</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>604</v>
+        <v>112</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -13100,21 +13077,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>605</v>
+        <v>643</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>605</v>
+        <v>643</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>83</v>
@@ -13126,20 +13103,18 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>606</v>
+        <v>116</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>607</v>
+        <v>117</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -13163,13 +13138,13 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>610</v>
+        <v>83</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>611</v>
+        <v>83</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -13187,31 +13162,31 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>605</v>
+        <v>122</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>612</v>
+        <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>613</v>
+        <v>83</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>522</v>
+        <v>112</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13222,14 +13197,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>614</v>
+        <v>644</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>614</v>
+        <v>644</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>83</v>
+        <v>581</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13242,25 +13217,25 @@
         <v>83</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>616</v>
+        <v>583</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>617</v>
+        <v>118</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>618</v>
+        <v>222</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13285,13 +13260,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>619</v>
+        <v>83</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>620</v>
+        <v>83</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13309,7 +13284,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>614</v>
+        <v>584</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13321,19 +13296,19 @@
         <v>83</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>612</v>
+        <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>613</v>
+        <v>83</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>522</v>
+        <v>198</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13342,12 +13317,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13355,32 +13330,34 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>622</v>
+        <v>264</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>647</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>648</v>
+      </c>
       <c r="O91" t="s" s="2">
-        <v>625</v>
+        <v>649</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13405,13 +13382,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13429,10 +13406,10 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>94</v>
@@ -13447,27 +13424,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>83</v>
+        <v>650</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>83</v>
+        <v>357</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>626</v>
+        <v>358</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>83</v>
+        <v>359</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13481,25 +13458,29 @@
         <v>94</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>108</v>
+        <v>652</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>654</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13523,13 +13504,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>83</v>
+        <v>656</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>83</v>
+        <v>657</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13547,7 +13528,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13556,7 +13537,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>83</v>
+        <v>658</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13565,27 +13546,27 @@
         <v>83</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>83</v>
+        <v>659</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>599</v>
+        <v>449</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>630</v>
+        <v>450</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>83</v>
+        <v>451</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13596,30 +13577,32 @@
         <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>632</v>
+        <v>264</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>634</v>
+        <v>662</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>663</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13643,13 +13626,13 @@
         <v>83</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>83</v>
+        <v>510</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13667,16 +13650,16 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>83</v>
+        <v>664</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>106</v>
@@ -13688,10 +13671,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>636</v>
+        <v>198</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>637</v>
+        <v>512</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13702,14 +13685,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>83</v>
+        <v>514</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13725,21 +13708,23 @@
         <v>83</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>639</v>
+        <v>264</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>640</v>
+        <v>515</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>641</v>
+        <v>516</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -13763,13 +13748,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>83</v>
+        <v>520</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13787,7 +13772,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13805,27 +13790,27 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>83</v>
+        <v>521</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>636</v>
+        <v>522</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>643</v>
+        <v>523</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>83</v>
+        <v>524</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13839,28 +13824,28 @@
         <v>82</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>579</v>
+        <v>84</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>645</v>
+        <v>667</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>645</v>
+        <v>668</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>646</v>
+        <v>573</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>647</v>
+        <v>574</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13909,7 +13894,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13921,7 +13906,7 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>648</v>
+        <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>83</v>
@@ -13930,1000 +13915,30 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>649</v>
+        <v>576</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>650</v>
+        <v>577</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP103" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP103">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AP95">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI102">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$103</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3675" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3979" uniqueCount="678">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profile for the FHIR Vital Sign Heart Rate Profile.
+    <t>French profiling of the FHIR Vital Sign Heart Rate Profile.
 Profilage français du profil Vital Signs Heart rate</t>
   </si>
   <si>
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/heartrate|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/heartrate</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -459,14 +459,14 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,9 +488,6 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-heartrate|2.2.0</t>
-  </si>
-  <si>
     <t>Observation.meta.security</t>
   </si>
   <si>
@@ -513,7 +510,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -537,7 +534,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -580,7 +577,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -656,15 +653,14 @@
     <t>levelOfExertion</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-level-of-exertion|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-level-of-exertion}
 </t>
   </si>
   <si>
     <t>FR Core Observation Level Of Exertion Extension</t>
   </si>
   <si>
-    <t>Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort).
-French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure</t>
+    <t>French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure | Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort)</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -677,15 +673,14 @@
     <t>bodyPosition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-position-ext|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-position-ext}
 </t>
   </si>
   <si>
     <t>FR Core Observation Body Position Ext Extension</t>
   </si>
   <si>
-    <t>Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.
-CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation</t>
+    <t>CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation | Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.</t>
   </si>
   <si>
     <t>Observation.extension:supportingInfo</t>
@@ -694,7 +689,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
+    <t xml:space="preserve">Extension {workflow-supportingInfo}
 </t>
   </si>
   <si>
@@ -755,7 +750,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -784,7 +779,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -864,7 +859,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1119,7 +1114,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1213,7 +1208,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1244,7 +1239,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1267,7 +1262,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
 </t>
   </si>
   <si>
@@ -1362,7 +1357,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
 </t>
   </si>
   <si>
@@ -1603,7 +1598,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t>obs-6
@@ -1635,7 +1630,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1688,7 +1683,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heartrate-body-location|2.2.0</t>
+    <t>http://hl7.org/fhir/hspc/ValueSet/heartRateMeasBodyLocationPrecoordVS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1703,6 +1698,21 @@
     <t>718497002 |Inherent location|</t>
   </si>
   <si>
+    <t>Observation.bodySite.id</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.coding</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heart-rate-body-position</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.text</t>
+  </si>
+  <si>
     <t>Observation.method</t>
   </si>
   <si>
@@ -1721,7 +1731,7 @@
     <t>Methods for heartrate observations.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heartrate-measurement-method|2.2.0</t>
+    <t>http://hl7.org/fhir/hspc/ValueSet/heartRateMeasMethodVS</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1730,10 +1740,25 @@
     <t>methodCode</t>
   </si>
   <si>
+    <t>Observation.method.id</t>
+  </si>
+  <si>
+    <t>Observation.method.extension</t>
+  </si>
+  <si>
+    <t>Observation.method.coding</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heart-rate-method</t>
+  </si>
+  <si>
+    <t>Observation.method.text</t>
+  </si>
+  <si>
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1761,7 +1786,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1841,7 +1866,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1891,7 +1916,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1924,7 +1949,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1961,7 +1986,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
 </t>
   </si>
   <si>
@@ -1983,7 +2008,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
 </t>
   </si>
   <si>
@@ -2429,18 +2454,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP95"/>
+  <dimension ref="A1:AP103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.12109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.9296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.5625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2451,28 +2476,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.26171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="33.30078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3729,7 +3754,7 @@
         <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>83</v>
@@ -3803,10 +3828,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3829,16 +3854,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3864,31 +3889,31 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3923,10 +3948,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3949,16 +3974,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3984,31 +4009,31 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -4043,10 +4068,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4072,13 +4097,13 @@
         <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4128,7 +4153,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4163,10 +4188,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4189,16 +4214,16 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4224,31 +4249,31 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4283,14 +4308,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4309,16 +4334,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4368,7 +4393,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4392,7 +4417,7 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
@@ -4403,14 +4428,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4429,16 +4454,16 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4488,7 +4513,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4512,7 +4537,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4523,10 +4548,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4552,10 +4577,10 @@
         <v>115</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4604,7 +4629,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4639,13 +4664,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>83</v>
@@ -4667,13 +4692,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4724,7 +4749,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4733,7 +4758,7 @@
         <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>123</v>
@@ -4759,13 +4784,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>83</v>
@@ -4787,13 +4812,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4844,7 +4869,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4853,7 +4878,7 @@
         <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>123</v>
@@ -4877,15 +4902,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>83</v>
@@ -4907,13 +4932,13 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4964,7 +4989,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4999,10 +5024,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5028,16 +5053,16 @@
         <v>115</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -5086,7 +5111,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5110,7 +5135,7 @@
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -5121,10 +5146,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5147,17 +5172,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -5206,7 +5231,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5221,19 +5246,19 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
@@ -5241,14 +5266,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5267,17 +5292,17 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5326,7 +5351,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5341,16 +5366,16 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5361,14 +5386,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5387,16 +5412,16 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5446,7 +5471,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5461,30 +5486,30 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AO25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5507,19 +5532,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5544,11 +5569,11 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5566,7 +5591,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>94</v>
@@ -5581,19 +5606,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
@@ -5601,10 +5626,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5627,19 +5652,19 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5664,19 +5689,19 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB27" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
@@ -5686,7 +5711,7 @@
         <v>121</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5710,24 +5735,24 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AP27" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
+      <c r="B28" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C28" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5749,19 +5774,19 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5786,14 +5811,14 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5810,7 +5835,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5834,10 +5859,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5845,10 +5870,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5963,10 +5988,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6081,12 +6106,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6109,19 +6134,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -6170,7 +6195,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6191,10 +6216,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6205,10 +6230,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6323,10 +6348,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6441,12 +6466,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6472,65 +6497,65 @@
         <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6551,10 +6576,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6565,10 +6590,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6594,13 +6619,13 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6650,7 +6675,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6671,24 +6696,24 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
+      <c r="B36" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6711,66 +6736,66 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6791,10 +6816,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6805,10 +6830,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6834,14 +6859,14 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6890,7 +6915,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6911,10 +6936,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6925,10 +6950,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6951,19 +6976,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -7012,7 +7037,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7033,10 +7058,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -7047,10 +7072,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7076,16 +7101,16 @@
         <v>108</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7134,7 +7159,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7155,28 +7180,28 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AO39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7195,19 +7220,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7232,14 +7257,14 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>354</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
       </c>
@@ -7256,7 +7281,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -7271,30 +7296,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7409,10 +7434,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7529,10 +7554,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7555,19 +7580,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7604,7 +7629,7 @@
         <v>83</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7614,7 +7639,7 @@
         <v>121</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7635,10 +7660,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7649,13 +7674,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C44" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>83</v>
@@ -7677,19 +7702,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7738,7 +7763,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7759,10 +7784,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7773,10 +7798,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7891,10 +7916,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8011,10 +8036,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8040,23 +8065,23 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -8098,7 +8123,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8119,10 +8144,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8133,10 +8158,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8162,13 +8187,13 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8218,7 +8243,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8239,10 +8264,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8253,10 +8278,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8279,24 +8304,24 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>83</v>
@@ -8338,7 +8363,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8359,10 +8384,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8373,10 +8398,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8402,14 +8427,14 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8458,7 +8483,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8479,10 +8504,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8493,10 +8518,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8519,19 +8544,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8580,7 +8605,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8601,10 +8626,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8615,10 +8640,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8644,16 +8669,16 @@
         <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8702,7 +8727,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8723,11 +8748,11 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AN52" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8735,12 +8760,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8763,19 +8788,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8824,7 +8849,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8839,19 +8864,19 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8859,10 +8884,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8885,16 +8910,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8944,7 +8969,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8965,13 +8990,13 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8979,14 +9004,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9005,19 +9030,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9066,7 +9091,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9081,34 +9106,34 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AO55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AP55" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9127,19 +9152,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9188,7 +9213,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9197,25 +9222,25 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AJ56" t="s" s="2">
+      <c r="AK56" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AK56" t="s" s="2">
+      <c r="AL56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9223,10 +9248,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9252,13 +9277,13 @@
         <v>130</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9308,7 +9333,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9329,13 +9354,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9343,10 +9368,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9369,17 +9394,17 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9428,7 +9453,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9443,19 +9468,19 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -9463,10 +9488,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9489,19 +9514,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9538,17 +9563,17 @@
         <v>83</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9557,7 +9582,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9566,30 +9591,30 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AO59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP59" t="s" s="2">
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
         <v>451</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
+      <c r="B60" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>83</v>
@@ -9611,19 +9636,19 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9672,7 +9697,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9681,7 +9706,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9690,27 +9715,27 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9825,10 +9850,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9943,12 +9968,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9971,19 +9996,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10032,7 +10057,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10053,10 +10078,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -10067,10 +10092,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10093,68 +10118,68 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q64" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="P64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q64" t="s" s="2">
+      <c r="R64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Y64" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="R64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="Y64" t="s" s="2">
+      <c r="Z64" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="Z64" t="s" s="2">
+      <c r="AA64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10175,24 +10200,24 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AO64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
+      <c r="B65" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10218,14 +10243,14 @@
         <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10274,7 +10299,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10295,24 +10320,24 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AO65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
+      <c r="B66" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10338,63 +10363,63 @@
         <v>136</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10403,7 +10428,7 @@
         <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>106</v>
@@ -10415,24 +10440,24 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AO66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
+      <c r="B67" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10455,68 +10480,68 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10537,24 +10562,24 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AN67" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AO67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>504</v>
-      </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10577,19 +10602,19 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10614,14 +10639,14 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
       </c>
@@ -10638,7 +10663,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10647,7 +10672,7 @@
         <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -10659,10 +10684,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10673,14 +10698,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10699,19 +10724,19 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10736,14 +10761,14 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10760,7 +10785,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10778,27 +10803,27 @@
         <v>83</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10821,19 +10846,19 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10882,7 +10907,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10903,10 +10928,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10917,10 +10942,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10943,16 +10968,16 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10978,11 +11003,11 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11000,7 +11025,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11018,27 +11043,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>541</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11061,20 +11086,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>264</v>
+        <v>108</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>543</v>
+        <v>109</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>83</v>
       </c>
@@ -11098,13 +11119,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>547</v>
+        <v>83</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>548</v>
+        <v>83</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -11122,7 +11143,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>542</v>
+        <v>111</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11134,7 +11155,7 @@
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -11143,10 +11164,10 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>549</v>
+        <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>550</v>
+        <v>112</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -11157,21 +11178,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>83</v>
@@ -11183,16 +11204,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>552</v>
+        <v>115</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>553</v>
+        <v>116</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>554</v>
+        <v>117</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>555</v>
+        <v>118</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11230,57 +11251,57 @@
         <v>83</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>551</v>
+        <v>122</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>556</v>
+        <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>557</v>
+        <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>558</v>
+        <v>112</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>559</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11291,7 +11312,7 @@
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
@@ -11300,21 +11321,23 @@
         <v>83</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>561</v>
+        <v>152</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>562</v>
+        <v>281</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>563</v>
+        <v>282</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
       </c>
@@ -11338,13 +11361,11 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>83</v>
+        <v>544</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11362,13 +11383,13 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>560</v>
+        <v>285</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>83</v>
@@ -11380,27 +11401,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>565</v>
+        <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>566</v>
+        <v>286</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>567</v>
+        <v>287</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>568</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11411,7 +11432,7 @@
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>83</v>
@@ -11420,22 +11441,22 @@
         <v>83</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>570</v>
+        <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>571</v>
+        <v>339</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>572</v>
+        <v>340</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>573</v>
+        <v>341</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>574</v>
+        <v>342</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11484,19 +11505,19 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>569</v>
+        <v>343</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>575</v>
+        <v>106</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>83</v>
@@ -11505,10 +11526,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>576</v>
+        <v>344</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>577</v>
+        <v>345</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11519,10 +11540,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>578</v>
+        <v>546</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>578</v>
+        <v>546</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11545,16 +11566,20 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>108</v>
+        <v>263</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>109</v>
+        <v>547</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
@@ -11578,13 +11603,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>83</v>
+        <v>551</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>83</v>
+        <v>552</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11602,7 +11627,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>111</v>
+        <v>546</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11614,7 +11639,7 @@
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
@@ -11623,10 +11648,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>83</v>
+        <v>553</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>112</v>
+        <v>554</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11637,21 +11662,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11663,17 +11688,15 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11722,19 +11745,19 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>83</v>
@@ -11757,14 +11780,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>581</v>
+        <v>114</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11777,26 +11800,24 @@
         <v>83</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>115</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>582</v>
+        <v>116</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>583</v>
+        <v>117</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="O78" t="s" s="2">
-        <v>222</v>
-      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11832,19 +11853,19 @@
         <v>83</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>584</v>
+        <v>122</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11868,7 +11889,7 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>198</v>
+        <v>112</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11879,10 +11900,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11893,7 +11914,7 @@
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>83</v>
@@ -11902,19 +11923,23 @@
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>586</v>
+        <v>152</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>587</v>
+        <v>281</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -11938,13 +11963,11 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>83</v>
+        <v>558</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -11962,16 +11985,16 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>585</v>
+        <v>285</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>589</v>
+        <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11983,10 +12006,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>590</v>
+        <v>286</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>591</v>
+        <v>287</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11997,10 +12020,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12020,19 +12043,23 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>586</v>
+        <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>593</v>
+        <v>339</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12080,7 +12107,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>592</v>
+        <v>343</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12089,7 +12116,7 @@
         <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>589</v>
+        <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>106</v>
@@ -12101,10 +12128,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>590</v>
+        <v>344</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>595</v>
+        <v>345</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12115,10 +12142,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>596</v>
+        <v>560</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>596</v>
+        <v>560</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12141,20 +12168,18 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>264</v>
+        <v>561</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>597</v>
+        <v>562</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>598</v>
+        <v>563</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
@@ -12178,13 +12203,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>601</v>
+        <v>83</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>602</v>
+        <v>83</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12202,7 +12227,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>596</v>
+        <v>560</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12220,27 +12245,27 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>603</v>
+        <v>565</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>604</v>
+        <v>566</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>83</v>
+        <v>568</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12251,7 +12276,7 @@
         <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>83</v>
@@ -12263,20 +12288,18 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>264</v>
+        <v>570</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>606</v>
+        <v>571</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>607</v>
+        <v>572</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -12300,13 +12323,13 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>610</v>
+        <v>83</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>611</v>
+        <v>83</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12324,13 +12347,13 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>83</v>
@@ -12342,27 +12365,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>603</v>
+        <v>574</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>604</v>
+        <v>575</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>523</v>
+        <v>576</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>83</v>
+        <v>577</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>612</v>
+        <v>578</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>612</v>
+        <v>578</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12373,7 +12396,7 @@
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12385,17 +12408,19 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>613</v>
+        <v>579</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>614</v>
+        <v>580</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="O83" t="s" s="2">
-        <v>616</v>
+        <v>583</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12444,19 +12469,19 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>612</v>
+        <v>578</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>106</v>
+        <v>584</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
@@ -12465,10 +12490,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>83</v>
+        <v>585</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>617</v>
+        <v>586</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12479,10 +12504,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>618</v>
+        <v>587</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>618</v>
+        <v>587</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12508,10 +12533,10 @@
         <v>108</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>619</v>
+        <v>109</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>620</v>
+        <v>110</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12562,7 +12587,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>618</v>
+        <v>111</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12574,7 +12599,7 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12583,10 +12608,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>590</v>
+        <v>83</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>621</v>
+        <v>112</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12597,14 +12622,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>622</v>
+        <v>588</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>622</v>
+        <v>588</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12620,19 +12645,19 @@
         <v>83</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>623</v>
+        <v>115</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>624</v>
+        <v>116</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>625</v>
+        <v>117</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>626</v>
+        <v>118</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12682,7 +12707,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>622</v>
+        <v>122</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12694,7 +12719,7 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
@@ -12703,10 +12728,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>627</v>
+        <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>628</v>
+        <v>112</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12717,14 +12742,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>629</v>
+        <v>589</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>629</v>
+        <v>589</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>83</v>
+        <v>590</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12737,24 +12762,26 @@
         <v>83</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>630</v>
+        <v>115</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>631</v>
+        <v>591</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12802,7 +12829,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>629</v>
+        <v>593</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12814,7 +12841,7 @@
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12823,10 +12850,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>627</v>
+        <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>634</v>
+        <v>197</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12835,12 +12862,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>635</v>
+        <v>594</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>635</v>
+        <v>594</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12851,32 +12878,28 @@
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>636</v>
+        <v>596</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -12924,19 +12947,19 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>635</v>
+        <v>594</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>83</v>
+        <v>598</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>639</v>
+        <v>106</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>83</v>
@@ -12945,10 +12968,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>640</v>
+        <v>599</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>641</v>
+        <v>600</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12959,10 +12982,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>642</v>
+        <v>601</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>642</v>
+        <v>601</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12985,13 +13008,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>108</v>
+        <v>595</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>109</v>
+        <v>602</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>110</v>
+        <v>603</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13042,7 +13065,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>111</v>
+        <v>601</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13051,10 +13074,10 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>83</v>
+        <v>598</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>83</v>
@@ -13063,10 +13086,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>83</v>
+        <v>599</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>112</v>
+        <v>604</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -13077,21 +13100,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>643</v>
+        <v>605</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>643</v>
+        <v>605</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>83</v>
@@ -13103,18 +13126,20 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>115</v>
+        <v>263</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>116</v>
+        <v>606</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>117</v>
+        <v>607</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -13138,13 +13163,13 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>83</v>
+        <v>610</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>83</v>
+        <v>611</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -13162,31 +13187,31 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>122</v>
+        <v>605</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>83</v>
+        <v>612</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>83</v>
+        <v>613</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>112</v>
+        <v>522</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13197,14 +13222,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>644</v>
+        <v>614</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>644</v>
+        <v>614</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>581</v>
+        <v>83</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13217,25 +13242,25 @@
         <v>83</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>115</v>
+        <v>263</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>582</v>
+        <v>615</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>118</v>
+        <v>617</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>222</v>
+        <v>618</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13260,13 +13285,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>83</v>
+        <v>619</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>83</v>
+        <v>620</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13284,7 +13309,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>584</v>
+        <v>614</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13296,19 +13321,19 @@
         <v>83</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>83</v>
+        <v>612</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>83</v>
+        <v>613</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>198</v>
+        <v>522</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13317,12 +13342,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>645</v>
+        <v>621</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>645</v>
+        <v>621</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13330,34 +13355,32 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>264</v>
+        <v>622</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>648</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>649</v>
+        <v>625</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13382,13 +13405,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>353</v>
+        <v>83</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>354</v>
+        <v>83</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13406,10 +13429,10 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>645</v>
+        <v>621</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>94</v>
@@ -13424,27 +13447,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>650</v>
+        <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>358</v>
+        <v>626</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13458,29 +13481,25 @@
         <v>94</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>652</v>
+        <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>653</v>
+        <v>628</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13504,13 +13523,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>656</v>
+        <v>83</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>657</v>
+        <v>83</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13528,7 +13547,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13537,7 +13556,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>658</v>
+        <v>83</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13546,27 +13565,27 @@
         <v>83</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>659</v>
+        <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>449</v>
+        <v>599</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>451</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>631</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>660</v>
+        <v>631</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13577,32 +13596,30 @@
         <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J93" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K93" t="s" s="2">
-        <v>264</v>
+        <v>632</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>661</v>
+        <v>633</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>662</v>
+        <v>634</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13626,13 +13643,13 @@
         <v>83</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>510</v>
+        <v>83</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13650,16 +13667,16 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>660</v>
+        <v>631</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>664</v>
+        <v>83</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>106</v>
@@ -13671,10 +13688,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>198</v>
+        <v>636</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>512</v>
+        <v>637</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13685,14 +13702,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>665</v>
+        <v>638</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>665</v>
+        <v>638</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>514</v>
+        <v>83</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13708,23 +13725,21 @@
         <v>83</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>264</v>
+        <v>639</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>515</v>
+        <v>640</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>516</v>
+        <v>641</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -13748,13 +13763,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>519</v>
+        <v>83</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>520</v>
+        <v>83</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13772,7 +13787,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>665</v>
+        <v>638</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13790,27 +13805,27 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>521</v>
+        <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>522</v>
+        <v>636</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>523</v>
+        <v>643</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>524</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>666</v>
+        <v>644</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>666</v>
+        <v>644</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13824,28 +13839,28 @@
         <v>82</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>84</v>
+        <v>579</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>667</v>
+        <v>645</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>668</v>
+        <v>645</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>573</v>
+        <v>646</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>574</v>
+        <v>647</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13894,7 +13909,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>666</v>
+        <v>644</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13906,39 +13921,1009 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP95" t="s" s="2">
+      <c r="AK99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP103" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP95">
-    <filterColumn colId="7">
+  <autoFilter ref="A1:AP103">
+    <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="27">
+    <filterColumn colId="26">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI94">
+  <conditionalFormatting sqref="A2:AI102">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3979" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3675" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profiling of the FHIR Vital Sign Heart Rate Profile.
+    <t>French profile for the FHIR Vital Sign Heart Rate Profile.
 Profilage français du profil Vital Signs Heart rate</t>
   </si>
   <si>
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/heartrate</t>
+    <t>http://hl7.org/fhir/StructureDefinition/heartrate|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -459,14 +459,14 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,6 +488,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-heartrate|2.2.0</t>
+  </si>
+  <si>
     <t>Observation.meta.security</t>
   </si>
   <si>
@@ -510,7 +513,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -534,7 +537,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -577,7 +580,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -653,14 +656,15 @@
     <t>levelOfExertion</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-level-of-exertion}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-level-of-exertion|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Observation Level Of Exertion Extension</t>
   </si>
   <si>
-    <t>French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure | Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort)</t>
+    <t>Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort).
+French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -673,14 +677,15 @@
     <t>bodyPosition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-position-ext}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-position-ext|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Observation Body Position Ext Extension</t>
   </si>
   <si>
-    <t>CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation | Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.</t>
+    <t>Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.
+CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation</t>
   </si>
   <si>
     <t>Observation.extension:supportingInfo</t>
@@ -689,7 +694,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
 </t>
   </si>
   <si>
@@ -750,7 +755,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -779,7 +784,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -859,7 +864,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1114,7 +1119,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1208,7 +1213,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1239,7 +1244,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1262,7 +1267,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -1357,7 +1362,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0)
 </t>
   </si>
   <si>
@@ -1598,7 +1603,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1630,7 +1635,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1683,7 +1688,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/hspc/ValueSet/heartRateMeasBodyLocationPrecoordVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heartrate-body-location|2.2.0</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1698,21 +1703,6 @@
     <t>718497002 |Inherent location|</t>
   </si>
   <si>
-    <t>Observation.bodySite.id</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heart-rate-body-position</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.text</t>
-  </si>
-  <si>
     <t>Observation.method</t>
   </si>
   <si>
@@ -1731,7 +1721,7 @@
     <t>Methods for heartrate observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/hspc/ValueSet/heartRateMeasMethodVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heartrate-measurement-method|2.2.0</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1740,25 +1730,10 @@
     <t>methodCode</t>
   </si>
   <si>
-    <t>Observation.method.id</t>
-  </si>
-  <si>
-    <t>Observation.method.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heart-rate-method</t>
-  </si>
-  <si>
-    <t>Observation.method.text</t>
-  </si>
-  <si>
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1786,7 +1761,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1866,7 +1841,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1916,7 +1891,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1949,7 +1924,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1986,7 +1961,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2008,7 +1983,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2454,18 +2429,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP103"/>
+  <dimension ref="A1:AP95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.9296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.5625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.12109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2476,28 +2451,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.26171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.984375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.30078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3754,7 +3729,7 @@
         <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>83</v>
@@ -3828,10 +3803,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3854,16 +3829,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3889,13 +3864,13 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>83</v>
@@ -3913,7 +3888,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3948,10 +3923,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3974,16 +3949,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4009,13 +3984,13 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>83</v>
@@ -4033,7 +4008,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -4068,10 +4043,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4097,13 +4072,13 @@
         <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4153,7 +4128,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4188,10 +4163,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4214,16 +4189,16 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4249,13 +4224,13 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
@@ -4273,7 +4248,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4308,14 +4283,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4334,16 +4309,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4393,7 +4368,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4417,7 +4392,7 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
@@ -4428,14 +4403,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4454,16 +4429,16 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4513,7 +4488,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4537,7 +4512,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4548,10 +4523,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4577,10 +4552,10 @@
         <v>115</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4629,7 +4604,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4664,13 +4639,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>83</v>
@@ -4692,13 +4667,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4749,7 +4724,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4758,7 +4733,7 @@
         <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>123</v>
@@ -4784,13 +4759,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>83</v>
@@ -4812,13 +4787,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4869,7 +4844,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4878,7 +4853,7 @@
         <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>123</v>
@@ -4902,15 +4877,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>83</v>
@@ -4932,13 +4907,13 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4989,7 +4964,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -5024,10 +4999,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5053,16 +5028,16 @@
         <v>115</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -5111,7 +5086,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5135,7 +5110,7 @@
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -5146,10 +5121,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5172,17 +5147,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -5231,7 +5206,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5246,19 +5221,19 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
@@ -5266,14 +5241,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5292,17 +5267,17 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5351,7 +5326,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5366,16 +5341,16 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5386,14 +5361,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5412,16 +5387,16 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5471,7 +5446,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5486,16 +5461,16 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5504,12 +5479,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5532,19 +5507,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5569,11 +5544,11 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5591,7 +5566,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>94</v>
@@ -5606,19 +5581,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
@@ -5626,10 +5601,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5652,19 +5627,19 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5689,19 +5664,19 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
@@ -5711,7 +5686,7 @@
         <v>121</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5735,24 +5710,24 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5774,19 +5749,19 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5811,13 +5786,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5835,7 +5810,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5859,10 +5834,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5870,10 +5845,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5988,10 +5963,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6106,12 +6081,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6134,19 +6109,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -6195,7 +6170,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6216,10 +6191,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6230,10 +6205,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6348,10 +6323,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6466,12 +6441,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6497,23 +6472,23 @@
         <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6555,7 +6530,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6576,10 +6551,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6590,10 +6565,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6619,13 +6594,13 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6675,7 +6650,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6696,10 +6671,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6708,12 +6683,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6736,24 +6711,24 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6795,7 +6770,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6816,10 +6791,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6830,10 +6805,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6859,14 +6834,14 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6915,7 +6890,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6936,10 +6911,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6950,10 +6925,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6976,19 +6951,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -7037,7 +7012,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7058,10 +7033,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -7072,10 +7047,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7101,16 +7076,16 @@
         <v>108</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7159,7 +7134,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7180,10 +7155,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -7192,16 +7167,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7220,19 +7195,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7257,13 +7232,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7281,7 +7256,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -7296,30 +7271,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7434,10 +7409,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7554,10 +7529,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7580,19 +7555,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7629,7 +7604,7 @@
         <v>83</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7639,7 +7614,7 @@
         <v>121</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7660,10 +7635,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7674,13 +7649,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>83</v>
@@ -7702,19 +7677,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7763,7 +7738,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7784,10 +7759,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7798,10 +7773,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7916,10 +7891,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8036,10 +8011,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8065,23 +8040,23 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -8123,7 +8098,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8144,10 +8119,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8158,10 +8133,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8187,13 +8162,13 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8243,7 +8218,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8264,10 +8239,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8278,10 +8253,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8304,24 +8279,24 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>83</v>
@@ -8363,7 +8338,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8384,10 +8359,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8398,10 +8373,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8427,14 +8402,14 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8483,7 +8458,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8504,10 +8479,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8518,10 +8493,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8544,19 +8519,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8605,7 +8580,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8626,10 +8601,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8640,10 +8615,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8669,16 +8644,16 @@
         <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8727,7 +8702,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8748,10 +8723,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8760,12 +8735,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8788,19 +8763,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8849,7 +8824,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8864,19 +8839,19 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8884,10 +8859,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8910,16 +8885,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8969,7 +8944,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8990,13 +8965,13 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -9004,14 +8979,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9030,19 +9005,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9091,7 +9066,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9106,34 +9081,34 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9152,19 +9127,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9213,7 +9188,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9222,25 +9197,25 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9248,10 +9223,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9277,13 +9252,13 @@
         <v>130</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9333,7 +9308,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9354,13 +9329,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9368,10 +9343,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9394,17 +9369,17 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9453,7 +9428,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9468,19 +9443,19 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -9488,10 +9463,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9514,19 +9489,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9563,17 +9538,17 @@
         <v>83</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9582,7 +9557,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9591,30 +9566,30 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>83</v>
@@ -9636,19 +9611,19 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9697,7 +9672,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9706,7 +9681,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9715,27 +9690,27 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9850,10 +9825,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9968,12 +9943,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9996,19 +9971,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10057,7 +10032,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10078,10 +10053,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -10092,10 +10067,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10118,23 +10093,23 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="R64" t="s" s="2">
         <v>83</v>
@@ -10155,13 +10130,13 @@
         <v>83</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -10179,7 +10154,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10200,10 +10175,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10212,12 +10187,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10243,14 +10218,14 @@
         <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10299,7 +10274,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10320,10 +10295,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10332,12 +10307,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10363,21 +10338,21 @@
         <v>136</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>83</v>
@@ -10419,7 +10394,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10428,7 +10403,7 @@
         <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>106</v>
@@ -10440,10 +10415,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10452,12 +10427,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10480,26 +10455,26 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>83</v>
@@ -10541,7 +10516,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10562,10 +10537,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10574,12 +10549,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10602,19 +10577,19 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10639,13 +10614,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10663,7 +10638,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10672,7 +10647,7 @@
         <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -10684,10 +10659,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10698,14 +10673,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10724,19 +10699,19 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10761,13 +10736,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10785,7 +10760,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10803,27 +10778,27 @@
         <v>83</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10846,19 +10821,19 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10907,7 +10882,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10928,10 +10903,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10942,10 +10917,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10968,16 +10943,16 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11003,11 +10978,11 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11025,7 +11000,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11043,27 +11018,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11086,16 +11061,20 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>108</v>
+        <v>264</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>109</v>
+        <v>543</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
       </c>
@@ -11119,13 +11098,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>83</v>
+        <v>548</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -11143,7 +11122,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>111</v>
+        <v>542</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11155,7 +11134,7 @@
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -11164,10 +11143,10 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>83</v>
+        <v>549</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>112</v>
+        <v>550</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -11178,21 +11157,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>83</v>
@@ -11204,16 +11183,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>115</v>
+        <v>552</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>116</v>
+        <v>553</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>117</v>
+        <v>554</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>118</v>
+        <v>555</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11251,57 +11230,57 @@
         <v>83</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>122</v>
+        <v>551</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>83</v>
+        <v>556</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>112</v>
+        <v>558</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>83</v>
+        <v>559</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11312,7 +11291,7 @@
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
@@ -11321,23 +11300,21 @@
         <v>83</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>152</v>
+        <v>561</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>281</v>
+        <v>562</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>282</v>
+        <v>563</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>83</v>
       </c>
@@ -11361,11 +11338,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11383,13 +11362,13 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>285</v>
+        <v>560</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>83</v>
@@ -11401,27 +11380,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>83</v>
+        <v>565</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>286</v>
+        <v>566</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>287</v>
+        <v>567</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>83</v>
+        <v>568</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11432,7 +11411,7 @@
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>83</v>
@@ -11441,22 +11420,22 @@
         <v>83</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>108</v>
+        <v>570</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>339</v>
+        <v>571</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>340</v>
+        <v>572</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>341</v>
+        <v>573</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>342</v>
+        <v>574</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11505,19 +11484,19 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>343</v>
+        <v>569</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>106</v>
+        <v>575</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>83</v>
@@ -11526,10 +11505,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>344</v>
+        <v>576</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>345</v>
+        <v>577</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11540,10 +11519,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11566,20 +11545,16 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>263</v>
+        <v>108</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>547</v>
+        <v>109</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
@@ -11603,13 +11578,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>551</v>
+        <v>83</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>552</v>
+        <v>83</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11627,7 +11602,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>546</v>
+        <v>111</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11639,7 +11614,7 @@
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
@@ -11648,10 +11623,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>553</v>
+        <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>554</v>
+        <v>112</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11662,21 +11637,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11688,15 +11663,17 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11745,19 +11722,19 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>83</v>
@@ -11780,14 +11757,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>556</v>
+        <v>580</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>556</v>
+        <v>580</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>114</v>
+        <v>581</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11800,24 +11777,26 @@
         <v>83</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>115</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>116</v>
+        <v>582</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>117</v>
+        <v>583</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11853,19 +11832,19 @@
         <v>83</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>122</v>
+        <v>584</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11889,7 +11868,7 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>112</v>
+        <v>198</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11900,10 +11879,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11914,7 +11893,7 @@
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>83</v>
@@ -11923,23 +11902,19 @@
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>152</v>
+        <v>586</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>281</v>
+        <v>587</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -11963,11 +11938,13 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>558</v>
+        <v>83</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -11985,16 +11962,16 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>285</v>
+        <v>585</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>83</v>
+        <v>589</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -12006,10 +11983,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>286</v>
+        <v>590</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>287</v>
+        <v>591</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -12020,10 +11997,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>559</v>
+        <v>592</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>559</v>
+        <v>592</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12043,23 +12020,19 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>108</v>
+        <v>586</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>339</v>
+        <v>593</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12107,7 +12080,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>343</v>
+        <v>592</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12116,7 +12089,7 @@
         <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>83</v>
+        <v>589</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>106</v>
@@ -12128,10 +12101,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>344</v>
+        <v>590</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>345</v>
+        <v>595</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12142,10 +12115,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12168,18 +12141,20 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>561</v>
+        <v>264</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>562</v>
+        <v>597</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>563</v>
+        <v>598</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
@@ -12203,13 +12178,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>83</v>
+        <v>601</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>83</v>
+        <v>602</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12227,7 +12202,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12245,27 +12220,27 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>565</v>
+        <v>603</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>566</v>
+        <v>604</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>567</v>
+        <v>523</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>568</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12276,7 +12251,7 @@
         <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>83</v>
@@ -12288,18 +12263,20 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>570</v>
+        <v>264</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>571</v>
+        <v>606</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>572</v>
+        <v>607</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -12323,13 +12300,13 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>83</v>
+        <v>610</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>83</v>
+        <v>611</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12347,13 +12324,13 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>83</v>
@@ -12365,27 +12342,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>574</v>
+        <v>603</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>575</v>
+        <v>604</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>576</v>
+        <v>523</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>577</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12396,7 +12373,7 @@
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12408,19 +12385,17 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>579</v>
+        <v>613</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>580</v>
+        <v>614</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12469,19 +12444,19 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>584</v>
+        <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
@@ -12490,10 +12465,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>585</v>
+        <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12504,10 +12479,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12533,10 +12508,10 @@
         <v>108</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>109</v>
+        <v>619</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>110</v>
+        <v>620</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12587,7 +12562,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>111</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12599,7 +12574,7 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12608,10 +12583,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>83</v>
+        <v>590</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>112</v>
+        <v>621</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12622,14 +12597,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>588</v>
+        <v>622</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>588</v>
+        <v>622</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12645,19 +12620,19 @@
         <v>83</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>115</v>
+        <v>623</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>116</v>
+        <v>624</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>117</v>
+        <v>625</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>118</v>
+        <v>626</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12707,7 +12682,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>122</v>
+        <v>622</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12719,7 +12694,7 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
@@ -12728,10 +12703,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>83</v>
+        <v>627</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>112</v>
+        <v>628</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12742,14 +12717,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>589</v>
+        <v>629</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>589</v>
+        <v>629</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>590</v>
+        <v>83</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12762,26 +12737,24 @@
         <v>83</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>115</v>
+        <v>630</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>591</v>
+        <v>631</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>592</v>
+        <v>632</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12829,7 +12802,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>593</v>
+        <v>629</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12841,7 +12814,7 @@
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12850,10 +12823,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>83</v>
+        <v>627</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>197</v>
+        <v>634</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12862,12 +12835,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12878,28 +12851,32 @@
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>596</v>
+        <v>636</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>636</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>638</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -12947,19 +12924,19 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>598</v>
+        <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>639</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>83</v>
@@ -12968,10 +12945,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>599</v>
+        <v>640</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>600</v>
+        <v>641</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12982,10 +12959,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>601</v>
+        <v>642</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>601</v>
+        <v>642</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13008,13 +12985,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>595</v>
+        <v>108</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>602</v>
+        <v>109</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>603</v>
+        <v>110</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13065,7 +13042,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>601</v>
+        <v>111</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13074,10 +13051,10 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>598</v>
+        <v>83</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>83</v>
@@ -13086,10 +13063,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>599</v>
+        <v>83</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>604</v>
+        <v>112</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -13100,21 +13077,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>605</v>
+        <v>643</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>605</v>
+        <v>643</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>83</v>
@@ -13126,20 +13103,18 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>606</v>
+        <v>116</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>607</v>
+        <v>117</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -13163,13 +13138,13 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>610</v>
+        <v>83</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>611</v>
+        <v>83</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -13187,31 +13162,31 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>605</v>
+        <v>122</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>612</v>
+        <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>613</v>
+        <v>83</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>522</v>
+        <v>112</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13222,14 +13197,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>614</v>
+        <v>644</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>614</v>
+        <v>644</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>83</v>
+        <v>581</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13242,25 +13217,25 @@
         <v>83</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>616</v>
+        <v>583</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>617</v>
+        <v>118</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>618</v>
+        <v>222</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13285,13 +13260,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>619</v>
+        <v>83</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>620</v>
+        <v>83</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13309,7 +13284,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>614</v>
+        <v>584</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13321,19 +13296,19 @@
         <v>83</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>612</v>
+        <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>613</v>
+        <v>83</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>522</v>
+        <v>198</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13342,12 +13317,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13355,32 +13330,34 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>622</v>
+        <v>264</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>647</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>648</v>
+      </c>
       <c r="O91" t="s" s="2">
-        <v>625</v>
+        <v>649</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13405,13 +13382,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13429,10 +13406,10 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>94</v>
@@ -13447,27 +13424,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>83</v>
+        <v>650</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>83</v>
+        <v>357</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>626</v>
+        <v>358</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>83</v>
+        <v>359</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13481,25 +13458,29 @@
         <v>94</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>108</v>
+        <v>652</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>654</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13523,13 +13504,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>83</v>
+        <v>656</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>83</v>
+        <v>657</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13547,7 +13528,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13556,7 +13537,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>83</v>
+        <v>658</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13565,27 +13546,27 @@
         <v>83</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>83</v>
+        <v>659</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>599</v>
+        <v>449</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>630</v>
+        <v>450</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>83</v>
+        <v>451</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13596,30 +13577,32 @@
         <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>632</v>
+        <v>264</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>634</v>
+        <v>662</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>663</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13643,13 +13626,13 @@
         <v>83</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>83</v>
+        <v>510</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13667,16 +13650,16 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>83</v>
+        <v>664</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>106</v>
@@ -13688,10 +13671,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>636</v>
+        <v>198</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>637</v>
+        <v>512</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13702,14 +13685,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>83</v>
+        <v>514</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13725,21 +13708,23 @@
         <v>83</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>639</v>
+        <v>264</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>640</v>
+        <v>515</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>641</v>
+        <v>516</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -13763,13 +13748,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>83</v>
+        <v>520</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13787,7 +13772,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13805,27 +13790,27 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>83</v>
+        <v>521</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>636</v>
+        <v>522</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>643</v>
+        <v>523</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>83</v>
+        <v>524</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13839,28 +13824,28 @@
         <v>82</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>579</v>
+        <v>84</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>645</v>
+        <v>667</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>645</v>
+        <v>668</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>646</v>
+        <v>573</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>647</v>
+        <v>574</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13909,7 +13894,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13921,7 +13906,7 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>648</v>
+        <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>83</v>
@@ -13930,1000 +13915,30 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>649</v>
+        <v>576</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>650</v>
+        <v>577</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP103" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP103">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AP95">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI102">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
